--- a/DB/news_data.xlsx
+++ b/DB/news_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
   <si>
     <t>Ticker</t>
   </si>
@@ -67,6 +67,30 @@
     <t>Sector Update: Tech Stocks Gain Thursday Afternoon</t>
   </si>
   <si>
+    <t>Is Apple Inc. (AAPL) the Most Profitable Tech Stock to Buy Now?</t>
+  </si>
+  <si>
+    <t>Cloud AI Today - Check Point Leads AI Cybersecurity With CloudGuard Advancements</t>
+  </si>
+  <si>
+    <t>Europe refuses to delay Meta and Apple antitrust decisions, despite pressure from the U.S.</t>
+  </si>
+  <si>
+    <t>Is Apple Stock A Buy Before New Product Reveal?</t>
+  </si>
+  <si>
+    <t>Warren Buffett's AI Bets: 24% of Berkshire Hathaway's $299 Billion Stock Portfolio Is in These 2 Artificial Intelligence Stocks</t>
+  </si>
+  <si>
+    <t>Should You Buy Apple Stock Hand Over Fist Before Feb. 19?</t>
+  </si>
+  <si>
+    <t>Huawei's tri-foldable phone hits global markets in a show of defiance amid US curbs</t>
+  </si>
+  <si>
+    <t>The 3 Best Stocks to Buy and Hold for the Next Stage of the Artificial Intelligence (AI) Revolution</t>
+  </si>
+  <si>
     <t>https://finance.yahoo.com/m/2a8d943e-8717-3a19-a01f-2189b195381d/apple%2C-google-restore%C2%A0tiktok.html</t>
   </si>
   <si>
@@ -91,6 +115,30 @@
     <t>https://finance.yahoo.com/news/sector-tech-stocks-gain-thursday-185630415.html</t>
   </si>
   <si>
+    <t>https://finance.yahoo.com/news/apple-inc-aapl-most-profitable-122451503.html</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/news/cloud-ai-today-check-point-120745016.html</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/m/3183603d-3400-39a0-8315-06b647fabd4f/europe-refuses-to-delay-meta.html</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/m/8d01c248-e1eb-3b60-aba6-7725d3fcda1d/is-apple-stock-a-buy-before.html</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/m/d6d44b83-f2b4-309d-8a3d-a545222a4913/warren-buffett%27s-ai-bets%3A-24%25.html</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/m/6111ff4a-1dcc-3fc2-a0e8-f9cd6cb34931/should-you-buy-apple-stock.html</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/m/1dfbb568-4f02-3460-9820-9e73c693e0c7/huawei%27s-tri-foldable-phone.html</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/m/b2484ac2-2ca7-3a8b-893f-a7904fbd10e1/the-3-best-stocks-to-buy-and.html</t>
+  </si>
+  <si>
     <t>2025-02-14 01:20:05 UTC</t>
   </si>
   <si>
@@ -115,6 +163,30 @@
     <t>2025-02-13 18:56:30 UTC</t>
   </si>
   <si>
+    <t>2025-02-18 12:24:51 UTC</t>
+  </si>
+  <si>
+    <t>2025-02-18 12:07:45 UTC</t>
+  </si>
+  <si>
+    <t>2025-02-18 11:13:33 UTC</t>
+  </si>
+  <si>
+    <t>2025-02-18 11:00:38 UTC</t>
+  </si>
+  <si>
+    <t>2025-02-18 10:45:00 UTC</t>
+  </si>
+  <si>
+    <t>2025-02-18 10:15:00 UTC</t>
+  </si>
+  <si>
+    <t>2025-02-18 09:56:32 UTC</t>
+  </si>
+  <si>
+    <t>2025-02-18 09:15:00 UTC</t>
+  </si>
+  <si>
     <t>Bloomberg</t>
   </si>
   <si>
@@ -137,6 +209,18 @@
   </si>
   <si>
     <t>MT Newswires</t>
+  </si>
+  <si>
+    <t>Simply Wall St.</t>
+  </si>
+  <si>
+    <t>Fortune</t>
+  </si>
+  <si>
+    <t>Motley Fool</t>
+  </si>
+  <si>
+    <t>Associated Press Finance</t>
   </si>
 </sst>
 </file>
@@ -507,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -535,13 +619,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -552,13 +636,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -569,13 +653,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -586,13 +670,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -603,13 +687,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -620,13 +704,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -637,13 +721,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -654,13 +738,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -671,13 +755,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -688,13 +772,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -705,13 +789,149 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
         <v>24</v>
       </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C20" s="2" t="s">
         <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -727,6 +947,14 @@
     <hyperlink ref="C10" r:id="rId9"/>
     <hyperlink ref="C11" r:id="rId10"/>
     <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C13" r:id="rId12"/>
+    <hyperlink ref="C14" r:id="rId13"/>
+    <hyperlink ref="C15" r:id="rId14"/>
+    <hyperlink ref="C16" r:id="rId15"/>
+    <hyperlink ref="C17" r:id="rId16"/>
+    <hyperlink ref="C18" r:id="rId17"/>
+    <hyperlink ref="C19" r:id="rId18"/>
+    <hyperlink ref="C20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
